--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:31</t>
+    <t xml:space="preserve">2026-09-12 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:47</t>
+    <t xml:space="preserve">2026-09-24 00:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:25</t>
+    <t xml:space="preserve">2026-09-27 22:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:14</t>
+    <t xml:space="preserve">2026-10-01 20:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:54</t>
+    <t xml:space="preserve">2026-10-02 13:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:12</t>
+    <t xml:space="preserve">2026-10-05 08:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
